--- a/Agile Info.xlsx
+++ b/Agile Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ea22cc3b98a8f61/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="211" documentId="8_{D7A608C0-7202-4A1E-BDD8-89236BB73791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8EF7AE14-F955-43A7-B69B-9348E3F29E3C}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{4C931056-3BFC-4CFE-B19C-539424B61F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1067DC5F-B600-4497-9B1C-3E1C99064CCF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -309,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="172">
   <si>
     <t>Planned Sprint</t>
   </si>
@@ -627,6 +627,204 @@
   </si>
   <si>
     <t>Stop skipping input validation during development.</t>
+  </si>
+  <si>
+    <t>US009</t>
+  </si>
+  <si>
+    <t>T08</t>
+  </si>
+  <si>
+    <t>Design Triage Agent rules: severity keyword sets, weighting logic, and confidence scoring approach</t>
+  </si>
+  <si>
+    <t>14-Jul-2026</t>
+  </si>
+  <si>
+    <t>Design</t>
+  </si>
+  <si>
+    <t>T09</t>
+  </si>
+  <si>
+    <t>Implement TriageAgent.classify() — severity scoring and Medium default fallback for weak signals</t>
+  </si>
+  <si>
+    <t>15-Jul-2026</t>
+  </si>
+  <si>
+    <t>T10</t>
+  </si>
+  <si>
+    <t>Implement priority mapping (P0-P3) and urgency-keyword priority bump logic</t>
+  </si>
+  <si>
+    <t>16-Jul-2026</t>
+  </si>
+  <si>
+    <t>T11</t>
+  </si>
+  <si>
+    <t>Implement component classification (Auth, Payments, DB, API, Frontend, etc.) via keyword scoring</t>
+  </si>
+  <si>
+    <t>17-Jul-2026</t>
+  </si>
+  <si>
+    <t>US010</t>
+  </si>
+  <si>
+    <t>T12</t>
+  </si>
+  <si>
+    <t>Add confidence score calculation and human-readable reasoning string to Triage Agent output</t>
+  </si>
+  <si>
+    <t>18-Jul-2026</t>
+  </si>
+  <si>
+    <t>US011</t>
+  </si>
+  <si>
+    <t>T13</t>
+  </si>
+  <si>
+    <t>Design Log Analysis Agent parsing rules for Python, Java, JS/Node and generic log formats</t>
+  </si>
+  <si>
+    <t>T14</t>
+  </si>
+  <si>
+    <t>Implement Python traceback parsing (exception type, message, last-frame failure point)</t>
+  </si>
+  <si>
+    <t>19-Jul-2026</t>
+  </si>
+  <si>
+    <t>T15</t>
+  </si>
+  <si>
+    <t>Implement Java stack trace and JS/Node runtime error parsing</t>
+  </si>
+  <si>
+    <t>20-Jul-2026</t>
+  </si>
+  <si>
+    <t>US012</t>
+  </si>
+  <si>
+    <t>T16</t>
+  </si>
+  <si>
+    <t>Extract affected code path(s) list and generate error signature hash for future duplicate detection</t>
+  </si>
+  <si>
+    <t>US013</t>
+  </si>
+  <si>
+    <t>T17</t>
+  </si>
+  <si>
+    <t>Build orchestrator to run Triage Agent and Log Analysis Agent together on every submission</t>
+  </si>
+  <si>
+    <t>21-Jul-2026</t>
+  </si>
+  <si>
+    <t>US014</t>
+  </si>
+  <si>
+    <t>T18</t>
+  </si>
+  <si>
+    <t>Add AgentAnalysis DB model and persist combined structured output keyed by bug_id</t>
+  </si>
+  <si>
+    <t>T19</t>
+  </si>
+  <si>
+    <t>Wire /api/bugs/paste and /api/bugs/upload to run analysis before save and return it in the response</t>
+  </si>
+  <si>
+    <t>22-Jul-2026</t>
+  </si>
+  <si>
+    <t>T20</t>
+  </si>
+  <si>
+    <t>Add GET /api/bugs/{id}/analysis endpoint and update frontend to show agent results in preview and history modal</t>
+  </si>
+  <si>
+    <t>US015</t>
+  </si>
+  <si>
+    <t>T21</t>
+  </si>
+  <si>
+    <t>Build seeded validation dataset with varied bug report styles and error types</t>
+  </si>
+  <si>
+    <t>23-Jul-2026</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>T22</t>
+  </si>
+  <si>
+    <t>Write validate_agents.py and run it to measure and report Triage/Log Analysis accuracy</t>
+  </si>
+  <si>
+    <t>Started on Triage Agent keyword rules using the design doc as reference.</t>
+  </si>
+  <si>
+    <t>Needed to decide how many keyword matches should count as "strong enough" evidence before bumping severity.</t>
+  </si>
+  <si>
+    <t>Added a minimum match-count threshold so a single incidental keyword no longer overrides the Medium default.</t>
+  </si>
+  <si>
+    <t>Log Analysis Agent regex for JS/Node errors was matching the wrong filename when the stack line had a nested function call.</t>
+  </si>
+  <si>
+    <t>Tightened the regex to prefer the file:line:col captured inside parentheses first.</t>
+  </si>
+  <si>
+    <t>Wiring the orchestrator into the existing paste/upload endpoints without breaking Milestone 1 behavior took longer than estimated.</t>
+  </si>
+  <si>
+    <t>Ran both agents before creating the DB record and reused the existing severity field instead of adding a new one.</t>
+  </si>
+  <si>
+    <t>Finished persisting combined agent output and added the /analysis endpoint.</t>
+  </si>
+  <si>
+    <t>Frontend history modal did not have a place to show agent results yet.</t>
+  </si>
+  <si>
+    <t>Added an Agent Analysis section to the modal and preview panel showing severity, confidence bar, and reasoning.</t>
+  </si>
+  <si>
+    <t>Needed realistic and varied sample bug reports to test accuracy, not just clean examples.</t>
+  </si>
+  <si>
+    <t>Built a seeded dataset covering Python, Java, JS, plain-text, and cosmetic/UI reports.</t>
+  </si>
+  <si>
+    <t>Ran validate_agents.py, reviewed misclassifications, and logged accuracy results for both agents.</t>
+  </si>
+  <si>
+    <t>Start writing small validation scripts alongside each agent instead of testing everything at the end.</t>
+  </si>
+  <si>
+    <t>Stop hardcoding confidence thresholds without checking them against real varied examples first.</t>
+  </si>
+  <si>
+    <t>Continue documenting reasoning strings so agent output stays explainable.</t>
+  </si>
+  <si>
+    <t>Added the seeded validation dataset and adjusted severity/confidence thresholds after reviewing accuracy results.</t>
   </si>
 </sst>
 </file>
@@ -1160,10 +1358,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
@@ -2065,63 +2259,63 @@
       <c r="H3" s="60"/>
       <c r="I3" s="25">
         <f t="shared" ref="I3:W3" si="0">SUM(I5:I802)</f>
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="J3" s="25">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K3" s="25">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L3" s="25">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M3" s="25">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="N3" s="25">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O3" s="25">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P3" s="25">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Q3" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R3" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S3" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T3" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U3" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V3" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W3" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:23" s="24" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2492,20 +2686,40 @@
       <c r="W12" s="34"/>
     </row>
     <row r="13" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="26"/>
-      <c r="B13" s="58"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
+      <c r="A13" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="D13" s="58" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" s="58" t="s">
+        <v>109</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G13" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="H13" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I13" s="33">
+        <v>4</v>
+      </c>
+      <c r="J13" s="33">
+        <v>4</v>
+      </c>
       <c r="K13" s="33"/>
       <c r="L13" s="33"/>
-      <c r="M13" s="34"/>
-      <c r="N13" s="34"/>
+      <c r="M13" s="33"/>
+      <c r="N13" s="33"/>
       <c r="O13" s="34"/>
       <c r="P13" s="34"/>
       <c r="Q13" s="34"/>
@@ -2517,20 +2731,40 @@
       <c r="W13" s="34"/>
     </row>
     <row r="14" spans="1:23" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="26"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="33"/>
+      <c r="A14" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="D14" s="58" t="s">
+        <v>113</v>
+      </c>
+      <c r="E14" s="58" t="s">
+        <v>113</v>
+      </c>
+      <c r="F14" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G14" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="H14" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I14" s="33">
+        <v>7</v>
+      </c>
       <c r="J14" s="33"/>
-      <c r="K14" s="33"/>
+      <c r="K14" s="33">
+        <v>7</v>
+      </c>
       <c r="L14" s="33"/>
-      <c r="M14" s="34"/>
-      <c r="N14" s="34"/>
+      <c r="M14" s="33"/>
+      <c r="N14" s="33"/>
       <c r="O14" s="34"/>
       <c r="P14" s="34"/>
       <c r="Q14" s="34"/>
@@ -2542,20 +2776,40 @@
       <c r="W14" s="34"/>
     </row>
     <row r="15" spans="1:23" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="26"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="33"/>
+      <c r="A15" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" s="58" t="s">
+        <v>116</v>
+      </c>
+      <c r="E15" s="58" t="s">
+        <v>116</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G15" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="H15" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I15" s="33">
+        <v>4</v>
+      </c>
       <c r="J15" s="33"/>
       <c r="K15" s="33"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
+      <c r="L15" s="33">
+        <v>4</v>
+      </c>
+      <c r="M15" s="33"/>
+      <c r="N15" s="33"/>
       <c r="O15" s="34"/>
       <c r="P15" s="34"/>
       <c r="Q15" s="34"/>
@@ -2567,20 +2821,40 @@
       <c r="W15" s="34"/>
     </row>
     <row r="16" spans="1:23" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="26"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="33"/>
+      <c r="A16" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="E16" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="F16" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G16" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="H16" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I16" s="33">
+        <v>5</v>
+      </c>
       <c r="J16" s="33"/>
       <c r="K16" s="33"/>
       <c r="L16" s="33"/>
-      <c r="M16" s="34"/>
-      <c r="N16" s="34"/>
+      <c r="M16" s="33">
+        <v>5</v>
+      </c>
+      <c r="N16" s="33"/>
       <c r="O16" s="34"/>
       <c r="P16" s="34"/>
       <c r="Q16" s="34"/>
@@ -2592,20 +2866,40 @@
       <c r="W16" s="34"/>
     </row>
     <row r="17" spans="1:23" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="26"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="33"/>
+      <c r="A17" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="D17" s="58" t="s">
+        <v>123</v>
+      </c>
+      <c r="E17" s="58" t="s">
+        <v>123</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G17" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="H17" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I17" s="33">
+        <v>5</v>
+      </c>
       <c r="J17" s="33"/>
       <c r="K17" s="33"/>
       <c r="L17" s="33"/>
-      <c r="M17" s="34"/>
-      <c r="N17" s="34"/>
+      <c r="M17" s="33"/>
+      <c r="N17" s="33">
+        <v>5</v>
+      </c>
       <c r="O17" s="34"/>
       <c r="P17" s="34"/>
       <c r="Q17" s="34"/>
@@ -2617,21 +2911,41 @@
       <c r="W17" s="34"/>
     </row>
     <row r="18" spans="1:23" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="26"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="33"/>
+      <c r="A18" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="D18" s="58" t="s">
+        <v>123</v>
+      </c>
+      <c r="E18" s="58" t="s">
+        <v>123</v>
+      </c>
+      <c r="F18" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G18" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="H18" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I18" s="33">
+        <v>3</v>
+      </c>
       <c r="J18" s="33"/>
       <c r="K18" s="33"/>
       <c r="L18" s="33"/>
-      <c r="M18" s="34"/>
-      <c r="N18" s="34"/>
-      <c r="O18" s="34"/>
+      <c r="M18" s="33"/>
+      <c r="N18" s="33"/>
+      <c r="O18" s="34">
+        <v>3</v>
+      </c>
       <c r="P18" s="34"/>
       <c r="Q18" s="34"/>
       <c r="R18" s="34"/>
@@ -2642,22 +2956,42 @@
       <c r="W18" s="34"/>
     </row>
     <row r="19" spans="1:23" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="26"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="33"/>
+      <c r="A19" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D19" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="E19" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G19" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="H19" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I19" s="33">
+        <v>6</v>
+      </c>
       <c r="J19" s="33"/>
       <c r="K19" s="33"/>
       <c r="L19" s="33"/>
-      <c r="M19" s="34"/>
-      <c r="N19" s="34"/>
+      <c r="M19" s="33"/>
+      <c r="N19" s="33"/>
       <c r="O19" s="34"/>
-      <c r="P19" s="34"/>
+      <c r="P19" s="34">
+        <v>6</v>
+      </c>
       <c r="Q19" s="34"/>
       <c r="R19" s="34"/>
       <c r="S19" s="34"/>
@@ -2667,23 +3001,43 @@
       <c r="W19" s="34"/>
     </row>
     <row r="20" spans="1:23" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="26"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="33"/>
+      <c r="A20" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="D20" s="58" t="s">
+        <v>132</v>
+      </c>
+      <c r="E20" s="58" t="s">
+        <v>132</v>
+      </c>
+      <c r="F20" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G20" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="H20" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I20" s="33">
+        <v>7</v>
+      </c>
       <c r="J20" s="33"/>
       <c r="K20" s="33"/>
       <c r="L20" s="33"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="34"/>
+      <c r="M20" s="33"/>
+      <c r="N20" s="33"/>
       <c r="O20" s="34"/>
       <c r="P20" s="34"/>
-      <c r="Q20" s="34"/>
+      <c r="Q20" s="34">
+        <v>7</v>
+      </c>
       <c r="R20" s="34"/>
       <c r="S20" s="34"/>
       <c r="T20" s="34"/>
@@ -2692,24 +3046,44 @@
       <c r="W20" s="34"/>
     </row>
     <row r="21" spans="1:23" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="26"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="33"/>
+      <c r="A21" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="B21" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="D21" s="58" t="s">
+        <v>132</v>
+      </c>
+      <c r="E21" s="58" t="s">
+        <v>132</v>
+      </c>
+      <c r="F21" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G21" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="H21" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I21" s="33">
+        <v>4</v>
+      </c>
       <c r="J21" s="33"/>
       <c r="K21" s="33"/>
       <c r="L21" s="33"/>
-      <c r="M21" s="34"/>
-      <c r="N21" s="34"/>
+      <c r="M21" s="33"/>
+      <c r="N21" s="33"/>
       <c r="O21" s="34"/>
       <c r="P21" s="34"/>
       <c r="Q21" s="34"/>
-      <c r="R21" s="34"/>
+      <c r="R21" s="34">
+        <v>4</v>
+      </c>
       <c r="S21" s="34"/>
       <c r="T21" s="34"/>
       <c r="U21" s="34"/>
@@ -2717,95 +3091,173 @@
       <c r="W21" s="34"/>
     </row>
     <row r="22" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="26"/>
-      <c r="B22" s="29"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="33"/>
+      <c r="A22" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="D22" s="58" t="s">
+        <v>139</v>
+      </c>
+      <c r="E22" s="58" t="s">
+        <v>139</v>
+      </c>
+      <c r="F22" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G22" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="H22" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I22" s="33">
+        <v>6</v>
+      </c>
       <c r="J22" s="33"/>
       <c r="K22" s="33"/>
       <c r="L22" s="33"/>
-      <c r="M22" s="34"/>
-      <c r="N22" s="34"/>
+      <c r="M22" s="33"/>
+      <c r="N22" s="33"/>
       <c r="O22" s="34"/>
       <c r="P22" s="34"/>
       <c r="Q22" s="34"/>
       <c r="R22" s="34"/>
-      <c r="S22" s="34"/>
+      <c r="S22" s="34">
+        <v>6</v>
+      </c>
       <c r="T22" s="34"/>
       <c r="U22" s="34"/>
       <c r="V22" s="34"/>
       <c r="W22" s="34"/>
     </row>
     <row r="23" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="26"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="32"/>
-      <c r="I23" s="33"/>
+      <c r="A23" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="D23" s="58" t="s">
+        <v>139</v>
+      </c>
+      <c r="E23" s="58" t="s">
+        <v>139</v>
+      </c>
+      <c r="F23" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="H23" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I23" s="33">
+        <v>4</v>
+      </c>
       <c r="J23" s="33"/>
       <c r="K23" s="33"/>
       <c r="L23" s="33"/>
-      <c r="M23" s="34"/>
-      <c r="N23" s="34"/>
+      <c r="M23" s="33"/>
+      <c r="N23" s="33"/>
       <c r="O23" s="34"/>
       <c r="P23" s="34"/>
       <c r="Q23" s="34"/>
       <c r="R23" s="34"/>
       <c r="S23" s="34"/>
-      <c r="T23" s="34"/>
+      <c r="T23" s="34">
+        <v>4</v>
+      </c>
       <c r="U23" s="34"/>
       <c r="V23" s="34"/>
       <c r="W23" s="34"/>
     </row>
     <row r="24" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="26"/>
-      <c r="B24" s="29"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="33"/>
+      <c r="A24" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="B24" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" s="58" t="s">
+        <v>145</v>
+      </c>
+      <c r="E24" s="58" t="s">
+        <v>145</v>
+      </c>
+      <c r="F24" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G24" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="H24" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I24" s="33">
+        <v>6</v>
+      </c>
       <c r="J24" s="33"/>
       <c r="K24" s="33"/>
       <c r="L24" s="33"/>
-      <c r="M24" s="34"/>
-      <c r="N24" s="34"/>
+      <c r="M24" s="33"/>
+      <c r="N24" s="33"/>
       <c r="O24" s="34"/>
       <c r="P24" s="34"/>
       <c r="Q24" s="34"/>
       <c r="R24" s="34"/>
       <c r="S24" s="34"/>
       <c r="T24" s="34"/>
-      <c r="U24" s="34"/>
+      <c r="U24" s="34">
+        <v>6</v>
+      </c>
       <c r="V24" s="34"/>
       <c r="W24" s="34"/>
     </row>
     <row r="25" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="26"/>
-      <c r="B25" s="29"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="33"/>
+      <c r="A25" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="B25" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D25" s="58" t="s">
+        <v>145</v>
+      </c>
+      <c r="E25" s="58" t="s">
+        <v>145</v>
+      </c>
+      <c r="F25" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G25" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="H25" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I25" s="33">
+        <v>5</v>
+      </c>
       <c r="J25" s="33"/>
       <c r="K25" s="33"/>
       <c r="L25" s="33"/>
-      <c r="M25" s="34"/>
-      <c r="N25" s="34"/>
+      <c r="M25" s="33"/>
+      <c r="N25" s="33"/>
       <c r="O25" s="34"/>
       <c r="P25" s="34"/>
       <c r="Q25" s="34"/>
@@ -2813,24 +3265,44 @@
       <c r="S25" s="34"/>
       <c r="T25" s="34"/>
       <c r="U25" s="34"/>
-      <c r="V25" s="34"/>
+      <c r="V25" s="34">
+        <v>5</v>
+      </c>
       <c r="W25" s="34"/>
     </row>
     <row r="26" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="26"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="34"/>
-      <c r="K26" s="34"/>
-      <c r="L26" s="34"/>
-      <c r="M26" s="34"/>
-      <c r="N26" s="34"/>
+      <c r="A26" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="B26" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="D26" s="58" t="s">
+        <v>151</v>
+      </c>
+      <c r="E26" s="58" t="s">
+        <v>151</v>
+      </c>
+      <c r="F26" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G26" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="H26" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I26" s="33">
+        <v>5</v>
+      </c>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
+      <c r="N26" s="33"/>
       <c r="O26" s="34"/>
       <c r="P26" s="34"/>
       <c r="Q26" s="34"/>
@@ -2839,23 +3311,43 @@
       <c r="T26" s="34"/>
       <c r="U26" s="34"/>
       <c r="V26" s="34"/>
-      <c r="W26" s="34"/>
+      <c r="W26" s="34">
+        <v>5</v>
+      </c>
     </row>
     <row r="27" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="26"/>
-      <c r="B27" s="27"/>
-      <c r="C27" s="35"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="33"/>
-      <c r="J27" s="34"/>
-      <c r="K27" s="34"/>
-      <c r="L27" s="34"/>
-      <c r="M27" s="34"/>
-      <c r="N27" s="34"/>
+      <c r="A27" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="B27" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="D27" s="58" t="s">
+        <v>151</v>
+      </c>
+      <c r="E27" s="58" t="s">
+        <v>151</v>
+      </c>
+      <c r="F27" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G27" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="H27" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I27" s="33">
+        <v>6</v>
+      </c>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
+      <c r="N27" s="33"/>
       <c r="O27" s="34"/>
       <c r="P27" s="34"/>
       <c r="Q27" s="34"/>
@@ -2864,7 +3356,9 @@
       <c r="T27" s="34"/>
       <c r="U27" s="34"/>
       <c r="V27" s="34"/>
-      <c r="W27" s="34"/>
+      <c r="W27" s="34">
+        <v>6</v>
+      </c>
     </row>
     <row r="28" spans="1:23" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="26"/>
@@ -4036,7 +4530,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="41.54296875" customWidth="1"/>
@@ -4132,22 +4626,110 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="45"/>
-      <c r="B7" s="45"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
+      <c r="A7" s="45">
+        <v>2</v>
+      </c>
+      <c r="B7" s="45">
+        <v>1</v>
+      </c>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="8" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="45"/>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
+      <c r="A8" s="45">
+        <v>2</v>
+      </c>
+      <c r="B8" s="45">
+        <v>2</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="D8" s="46" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="9" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="45"/>
-      <c r="B9" s="45"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
+      <c r="A9" s="45">
+        <v>2</v>
+      </c>
+      <c r="B9" s="45">
+        <v>3</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>158</v>
+      </c>
+      <c r="D9" s="46" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="45">
+        <v>2</v>
+      </c>
+      <c r="B10" s="45">
+        <v>4</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="45">
+        <v>2</v>
+      </c>
+      <c r="B11" s="45">
+        <v>5</v>
+      </c>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="45">
+        <v>2</v>
+      </c>
+      <c r="B12" s="45">
+        <v>6</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>163</v>
+      </c>
+      <c r="D12" s="46" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="45">
+        <v>2</v>
+      </c>
+      <c r="B13" s="45">
+        <v>7</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>165</v>
+      </c>
+      <c r="D13" s="46" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="45">
+        <v>2</v>
+      </c>
+      <c r="B14" s="45">
+        <v>8</v>
+      </c>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46" t="s">
+        <v>167</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4232,14 +4814,30 @@
       <c r="A3" s="52">
         <v>2</v>
       </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
+      <c r="B3" s="52">
+        <v>2</v>
+      </c>
+      <c r="C3" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="52" t="s">
+        <v>151</v>
+      </c>
+      <c r="E3" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="F3" s="52" t="s">
+        <v>168</v>
+      </c>
+      <c r="G3" s="54" t="s">
+        <v>169</v>
+      </c>
+      <c r="H3" s="47" t="s">
+        <v>170</v>
+      </c>
+      <c r="I3" s="53" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="4" spans="1:9" s="47" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="52">

--- a/Agile Info.xlsx
+++ b/Agile Info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ea22cc3b98a8f61/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{4C931056-3BFC-4CFE-B19C-539424B61F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1067DC5F-B600-4497-9B1C-3E1C99064CCF}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="8_{622383C7-8DF1-4113-B351-BE0DC2D0EF10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA728788-0CAB-4087-A332-6D494F4ACCA7}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Product Backlog" sheetId="1" r:id="rId1"/>
@@ -47,9 +47,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
@@ -309,7 +306,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="240">
   <si>
     <t>Planned Sprint</t>
   </si>
@@ -825,6 +822,210 @@
   </si>
   <si>
     <t>Added the seeded validation dataset and adjusted severity/confidence thresholds after reviewing accuracy results.</t>
+  </si>
+  <si>
+    <t>As a developer, I would like the system to fetch similar historical defects using the RAG based retrieval in order to be able to propose a hypothesis for the root causes.</t>
+  </si>
+  <si>
+    <t>I want the Root Cause Agent to produce a level of confidence, and supporting historical evidence, in addition to the hypothesis, as a developer.</t>
+  </si>
+  <si>
+    <t>As a developer, I wish I had a Duplicate Detection Agent to have scanned past bugs and the history of the KB for any duplicates.</t>
+  </si>
+  <si>
+    <t>For a developer, there is a need to get the similarity scores and resolution summaries when duplicate matches are present.</t>
+  </si>
+  <si>
+    <t>As a developer, I want a Remediation Agent to provide me with suggestions for fixes based on previous solutions and root cause analysis.</t>
+  </si>
+  <si>
+    <t>As a developer, I want remediation suggestions to contain best-practices and confidence scoring.</t>
+  </si>
+  <si>
+    <t>As a developer, I want to see a Structured Findings Dashboard with all of the above elements in one.</t>
+  </si>
+  <si>
+    <t>As a developer I would like to populate a historical defect knowledge base for the agents to look up against.</t>
+  </si>
+  <si>
+    <t>US016</t>
+  </si>
+  <si>
+    <t>US017</t>
+  </si>
+  <si>
+    <t>US018</t>
+  </si>
+  <si>
+    <t>US019</t>
+  </si>
+  <si>
+    <t>US020</t>
+  </si>
+  <si>
+    <t>US021</t>
+  </si>
+  <si>
+    <t>US022</t>
+  </si>
+  <si>
+    <t>US023</t>
+  </si>
+  <si>
+    <t>Should</t>
+  </si>
+  <si>
+    <t>Create a TF-IDF + Cosine Similarity indexer (no external vector DB – all pure Python)</t>
+  </si>
+  <si>
+    <t>Seed knowledge base table for defectories of representative defects from components</t>
+  </si>
+  <si>
+    <t>Implement RootCauseAgent: get top-k historical matches and create root cause query from Triage + Log Analysis output</t>
+  </si>
+  <si>
+    <t>Implement DuplicateDetectionAgent: Create Combined Corpus from Historical KB and previous live submissions</t>
+  </si>
+  <si>
+    <t>Include similarity threshold filtering and resolution summary lookup for duplicate matches.</t>
+  </si>
+  <si>
+    <t>For RemediationAgent: collect context for Triage/Log/Root Cause/Duplicate and choose best-practice playbook per component</t>
+  </si>
+  <si>
+    <t>Add remediation grounding sources, confidence blending and step de-duplication logic</t>
+  </si>
+  <si>
+    <t>To execute all 5 Agents per submission and persist combined AgentAnalysis record, extend Orchestrator to run all 5 agents.</t>
+  </si>
+  <si>
+    <t>Create dashboard rendering of Root Cause evidence cards and Duplicate match cards, using similarity pills.</t>
+  </si>
+  <si>
+    <t>T23</t>
+  </si>
+  <si>
+    <t>T24</t>
+  </si>
+  <si>
+    <t>T25</t>
+  </si>
+  <si>
+    <t>T26</t>
+  </si>
+  <si>
+    <t>T27</t>
+  </si>
+  <si>
+    <t>T28</t>
+  </si>
+  <si>
+    <t>T29</t>
+  </si>
+  <si>
+    <t>T30</t>
+  </si>
+  <si>
+    <t>T31</t>
+  </si>
+  <si>
+    <t>T32</t>
+  </si>
+  <si>
+    <t>T33</t>
+  </si>
+  <si>
+    <t>T34</t>
+  </si>
+  <si>
+    <t>T35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with confidence scoring and reasoning string for implementing root cause hypothesis synthesis </t>
+  </si>
+  <si>
+    <t xml:space="preserve">To document 5-agent Structured Findings Dashboard </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starts the Structured Findings Dashboard layout </t>
+  </si>
+  <si>
+    <t>24-Jul-2026</t>
+  </si>
+  <si>
+    <t>25-Jul-2026</t>
+  </si>
+  <si>
+    <t>26-Jul-2026</t>
+  </si>
+  <si>
+    <t>27-Jul-2026</t>
+  </si>
+  <si>
+    <t>28-Jul-2026</t>
+  </si>
+  <si>
+    <t>29-Jul-2026</t>
+  </si>
+  <si>
+    <t>30-Jul-2026</t>
+  </si>
+  <si>
+    <t>31-Jul-2026</t>
+  </si>
+  <si>
+    <t>Copy the following functions</t>
+  </si>
+  <si>
+    <t>Unclear how many top-k matches to retrieve for a useful but not noisy root cause hypothesis.</t>
+  </si>
+  <si>
+    <t>Duplicate Detection Agent was returning too many low-similarity noise matches from short bug titles.</t>
+  </si>
+  <si>
+    <t>Remediation Agent recommendations sometimes repeated the same step from both duplicate and root cause context.</t>
+  </si>
+  <si>
+    <t>Needed a consistent way to trace which recommendations came from historical data vs best-practice rules.</t>
+  </si>
+  <si>
+    <t>Dashboard was becoming cluttered trying to show 5 agent sections on one panel.</t>
+  </si>
+  <si>
+    <t>Started building the TF-IDF similarity utility and seeding the historical defect KB.</t>
+  </si>
+  <si>
+    <t>Settled on top-3 matches with strong/weak similarity thresholds (0.35 / 0.15).</t>
+  </si>
+  <si>
+    <t>Added a 0.20 similarity threshold to filter out weak duplicate candidates.</t>
+  </si>
+  <si>
+    <t>Added step de-duplication while preserving priority order.</t>
+  </si>
+  <si>
+    <t>Added a sources list to Remediation output recording every grounding reference.</t>
+  </si>
+  <si>
+    <t>Finished the Orchestrator changes to run all 5 agents and persist one combined AgentAnalysis record.</t>
+  </si>
+  <si>
+    <t>Split the dashboard into clearly separated, color-coded sections per agent with confidence bars.</t>
+  </si>
+  <si>
+    <t>Completed dashboard wiring for both the live preview and the history detail modal.</t>
+  </si>
+  <si>
+    <t>Start designing similarity thresholds against sample data before hardcoding them into agents.</t>
+  </si>
+  <si>
+    <t>Continue tracing every recommendation back to its grounding source for explainability.</t>
+  </si>
+  <si>
+    <t>Tuned similarity thresholds against real seeded data and standardized dashboard section styling across all 5 agents.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">              Done</t>
   </si>
 </sst>
 </file>
@@ -1130,7 +1331,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
@@ -1320,6 +1521,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1356,6 +1560,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1714,84 +1922,212 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+      <c r="A10" s="3">
+        <v>3</v>
+      </c>
+      <c r="B10" s="3">
+        <v>3</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" s="57" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="11" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
+      <c r="A11" s="3">
+        <v>3</v>
+      </c>
+      <c r="B11" s="3">
+        <v>3</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H11" s="57" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="12" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
+      <c r="A12" s="3">
+        <v>3</v>
+      </c>
+      <c r="B12" s="3">
+        <v>3</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12" s="57" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="13" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
+      <c r="A13" s="3">
+        <v>3</v>
+      </c>
+      <c r="B13" s="3">
+        <v>3</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H13" s="57" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="14" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
+      <c r="A14" s="3">
+        <v>3</v>
+      </c>
+      <c r="B14" s="3">
+        <v>3</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" s="57" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
+      <c r="A15" s="3">
+        <v>3</v>
+      </c>
+      <c r="B15" s="3">
+        <v>3</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="57" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="16" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-    </row>
-    <row r="17" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
+      <c r="A16" s="3">
+        <v>3</v>
+      </c>
+      <c r="B16" s="3">
+        <v>3</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H16" s="57" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <v>3</v>
+      </c>
+      <c r="B17" s="3">
+        <v>3</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H17" s="57" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="18" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8"/>
@@ -2178,28 +2514,28 @@
       <c r="W1" s="21"/>
     </row>
     <row r="2" spans="1:23" s="24" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="63" t="s">
+      <c r="B2" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="60" t="s">
+      <c r="C2" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="60" t="s">
+      <c r="D2" s="61" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="64" t="s">
+      <c r="E2" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="60" t="s">
+      <c r="F2" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="60" t="s">
+      <c r="G2" s="61" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="60" t="s">
+      <c r="H2" s="61" t="s">
         <v>7</v>
       </c>
       <c r="I2" s="22" t="s">
@@ -2249,17 +2585,17 @@
       </c>
     </row>
     <row r="3" spans="1:23" s="24" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="62"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
+      <c r="A3" s="63"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
       <c r="I3" s="25">
         <f t="shared" ref="I3:W3" si="0">SUM(I5:I802)</f>
-        <v>120</v>
+        <v>192</v>
       </c>
       <c r="J3" s="25">
         <f t="shared" si="0"/>
@@ -2319,31 +2655,31 @@
       </c>
     </row>
     <row r="4" spans="1:23" s="24" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="61" t="s">
+      <c r="A4" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="61"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="61"/>
-      <c r="J4" s="61"/>
-      <c r="K4" s="61"/>
-      <c r="L4" s="61"/>
-      <c r="M4" s="61"/>
-      <c r="N4" s="61"/>
-      <c r="O4" s="61"/>
-      <c r="P4" s="61"/>
-      <c r="Q4" s="61"/>
-      <c r="R4" s="61"/>
-      <c r="S4" s="61"/>
-      <c r="T4" s="61"/>
-      <c r="U4" s="61"/>
-      <c r="V4" s="61"/>
-      <c r="W4" s="61"/>
+      <c r="B4" s="62"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="62"/>
+      <c r="L4" s="62"/>
+      <c r="M4" s="62"/>
+      <c r="N4" s="62"/>
+      <c r="O4" s="62"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="62"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="62"/>
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="62"/>
+      <c r="W4" s="62"/>
     </row>
     <row r="5" spans="1:23" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26"/>
@@ -3361,17 +3697,33 @@
       </c>
     </row>
     <row r="28" spans="1:23" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="26"/>
-      <c r="B28" s="27"/>
+      <c r="A28" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="B28" s="27" t="s">
+        <v>198</v>
+      </c>
       <c r="C28" s="35" t="s">
-        <v>67</v>
-      </c>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="33"/>
+        <v>189</v>
+      </c>
+      <c r="D28" s="58" t="s">
+        <v>214</v>
+      </c>
+      <c r="E28" s="58" t="s">
+        <v>214</v>
+      </c>
+      <c r="F28" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G28" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="H28" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I28" s="33">
+        <v>6</v>
+      </c>
       <c r="J28" s="34"/>
       <c r="K28" s="34"/>
       <c r="L28" s="34"/>
@@ -3388,17 +3740,33 @@
       <c r="W28" s="34"/>
     </row>
     <row r="29" spans="1:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="26"/>
-      <c r="B29" s="27"/>
+      <c r="A29" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="B29" s="27" t="s">
+        <v>199</v>
+      </c>
       <c r="C29" s="35" t="s">
-        <v>67</v>
-      </c>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="33"/>
+        <v>190</v>
+      </c>
+      <c r="D29" s="58" t="s">
+        <v>214</v>
+      </c>
+      <c r="E29" s="58" t="s">
+        <v>215</v>
+      </c>
+      <c r="F29" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G29" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="H29" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I29" s="33">
+        <v>5</v>
+      </c>
       <c r="J29" s="34"/>
       <c r="K29" s="34"/>
       <c r="L29" s="34"/>
@@ -3415,15 +3783,33 @@
       <c r="W29" s="34"/>
     </row>
     <row r="30" spans="1:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="26"/>
-      <c r="B30" s="27"/>
-      <c r="C30" s="35"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="33"/>
+      <c r="A30" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="B30" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="C30" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="D30" s="58" t="s">
+        <v>215</v>
+      </c>
+      <c r="E30" s="58" t="s">
+        <v>215</v>
+      </c>
+      <c r="F30" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G30" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="H30" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I30" s="33">
+        <v>7</v>
+      </c>
       <c r="J30" s="34"/>
       <c r="K30" s="34"/>
       <c r="L30" s="34"/>
@@ -3440,15 +3826,33 @@
       <c r="W30" s="34"/>
     </row>
     <row r="31" spans="1:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="26"/>
-      <c r="B31" s="27"/>
-      <c r="C31" s="35"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="33"/>
+      <c r="A31" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="B31" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="C31" s="35" t="s">
+        <v>211</v>
+      </c>
+      <c r="D31" s="58" t="s">
+        <v>215</v>
+      </c>
+      <c r="E31" s="58" t="s">
+        <v>216</v>
+      </c>
+      <c r="F31" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G31" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="H31" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I31" s="33">
+        <v>6</v>
+      </c>
       <c r="J31" s="34"/>
       <c r="K31" s="34"/>
       <c r="L31" s="34"/>
@@ -3465,15 +3869,33 @@
       <c r="W31" s="34"/>
     </row>
     <row r="32" spans="1:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="26"/>
-      <c r="B32" s="27"/>
-      <c r="C32" s="35"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="33"/>
+      <c r="A32" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="C32" s="35" t="s">
+        <v>192</v>
+      </c>
+      <c r="D32" s="58" t="s">
+        <v>216</v>
+      </c>
+      <c r="E32" s="58" t="s">
+        <v>216</v>
+      </c>
+      <c r="F32" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="H32" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I32" s="33">
+        <v>6</v>
+      </c>
       <c r="J32" s="34"/>
       <c r="K32" s="34"/>
       <c r="L32" s="34"/>
@@ -3490,15 +3912,33 @@
       <c r="W32" s="34"/>
     </row>
     <row r="33" spans="1:23" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="26"/>
-      <c r="B33" s="27"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="33"/>
+      <c r="A33" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="C33" s="35" t="s">
+        <v>193</v>
+      </c>
+      <c r="D33" s="58" t="s">
+        <v>216</v>
+      </c>
+      <c r="E33" s="58" t="s">
+        <v>217</v>
+      </c>
+      <c r="F33" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="H33" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I33" s="33">
+        <v>4</v>
+      </c>
       <c r="J33" s="34"/>
       <c r="K33" s="34"/>
       <c r="L33" s="34"/>
@@ -3515,17 +3955,33 @@
       <c r="W33" s="34"/>
     </row>
     <row r="34" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="26"/>
-      <c r="B34" s="27"/>
+      <c r="A34" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="B34" s="27" t="s">
+        <v>204</v>
+      </c>
       <c r="C34" s="35" t="s">
-        <v>67</v>
-      </c>
-      <c r="D34" s="29"/>
-      <c r="E34" s="29"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="33"/>
+        <v>194</v>
+      </c>
+      <c r="D34" s="58" t="s">
+        <v>217</v>
+      </c>
+      <c r="E34" s="58" t="s">
+        <v>217</v>
+      </c>
+      <c r="F34" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="H34" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I34" s="33">
+        <v>7</v>
+      </c>
       <c r="J34" s="34"/>
       <c r="K34" s="34"/>
       <c r="L34" s="34"/>
@@ -3542,17 +3998,33 @@
       <c r="W34" s="34"/>
     </row>
     <row r="35" spans="1:23" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="26"/>
-      <c r="B35" s="27"/>
+      <c r="A35" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="B35" s="27" t="s">
+        <v>205</v>
+      </c>
       <c r="C35" s="35" t="s">
-        <v>67</v>
-      </c>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="32"/>
-      <c r="I35" s="33"/>
+        <v>195</v>
+      </c>
+      <c r="D35" s="58" t="s">
+        <v>217</v>
+      </c>
+      <c r="E35" s="58" t="s">
+        <v>218</v>
+      </c>
+      <c r="F35" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="H35" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I35" s="33">
+        <v>5</v>
+      </c>
       <c r="J35" s="34"/>
       <c r="K35" s="34"/>
       <c r="L35" s="34"/>
@@ -3569,17 +4041,33 @@
       <c r="W35" s="34"/>
     </row>
     <row r="36" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="26"/>
-      <c r="B36" s="27"/>
+      <c r="A36" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="B36" s="27" t="s">
+        <v>206</v>
+      </c>
       <c r="C36" s="35" t="s">
-        <v>67</v>
-      </c>
-      <c r="D36" s="29"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="33"/>
+        <v>196</v>
+      </c>
+      <c r="D36" s="58" t="s">
+        <v>218</v>
+      </c>
+      <c r="E36" s="58" t="s">
+        <v>218</v>
+      </c>
+      <c r="F36" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="H36" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I36" s="33">
+        <v>6</v>
+      </c>
       <c r="J36" s="34"/>
       <c r="K36" s="34"/>
       <c r="L36" s="34"/>
@@ -3596,15 +4084,33 @@
       <c r="W36" s="34"/>
     </row>
     <row r="37" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="26"/>
-      <c r="B37" s="27"/>
-      <c r="C37" s="35"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="32"/>
-      <c r="I37" s="33"/>
+      <c r="A37" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="B37" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="C37" s="35" t="s">
+        <v>213</v>
+      </c>
+      <c r="D37" s="58" t="s">
+        <v>218</v>
+      </c>
+      <c r="E37" s="58" t="s">
+        <v>219</v>
+      </c>
+      <c r="F37" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G37" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="H37" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I37" s="33">
+        <v>5</v>
+      </c>
       <c r="J37" s="34"/>
       <c r="K37" s="34"/>
       <c r="L37" s="34"/>
@@ -3621,15 +4127,33 @@
       <c r="W37" s="34"/>
     </row>
     <row r="38" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="26"/>
-      <c r="B38" s="27"/>
-      <c r="C38" s="35"/>
-      <c r="D38" s="29"/>
-      <c r="E38" s="29"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="31"/>
-      <c r="H38" s="32"/>
-      <c r="I38" s="33"/>
+      <c r="A38" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="B38" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="C38" s="35" t="s">
+        <v>197</v>
+      </c>
+      <c r="D38" s="58" t="s">
+        <v>219</v>
+      </c>
+      <c r="E38" s="58" t="s">
+        <v>219</v>
+      </c>
+      <c r="F38" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G38" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="H38" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I38" s="33">
+        <v>6</v>
+      </c>
       <c r="J38" s="34"/>
       <c r="K38" s="34"/>
       <c r="L38" s="34"/>
@@ -3646,15 +4170,33 @@
       <c r="W38" s="34"/>
     </row>
     <row r="39" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="26"/>
-      <c r="B39" s="27"/>
-      <c r="C39" s="35"/>
-      <c r="D39" s="29"/>
-      <c r="E39" s="29"/>
-      <c r="F39" s="30"/>
-      <c r="G39" s="31"/>
-      <c r="H39" s="32"/>
-      <c r="I39" s="33"/>
+      <c r="A39" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="B39" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="C39" s="35" t="s">
+        <v>222</v>
+      </c>
+      <c r="D39" s="58" t="s">
+        <v>219</v>
+      </c>
+      <c r="E39" s="58" t="s">
+        <v>220</v>
+      </c>
+      <c r="F39" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G39" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="H39" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I39" s="33">
+        <v>5</v>
+      </c>
       <c r="J39" s="34"/>
       <c r="K39" s="34"/>
       <c r="L39" s="34"/>
@@ -3671,15 +4213,33 @@
       <c r="W39" s="34"/>
     </row>
     <row r="40" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="26"/>
-      <c r="B40" s="27"/>
-      <c r="C40" s="35"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="31"/>
-      <c r="H40" s="32"/>
-      <c r="I40" s="33"/>
+      <c r="A40" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="B40" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="C40" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="D40" s="58" t="s">
+        <v>220</v>
+      </c>
+      <c r="E40" s="58" t="s">
+        <v>221</v>
+      </c>
+      <c r="F40" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G40" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="H40" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I40" s="33">
+        <v>4</v>
+      </c>
       <c r="J40" s="34"/>
       <c r="K40" s="34"/>
       <c r="L40" s="34"/>
@@ -3701,8 +4261,8 @@
       <c r="C41" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="D41" s="29"/>
-      <c r="E41" s="29"/>
+      <c r="D41" s="58"/>
+      <c r="E41" s="58"/>
       <c r="F41" s="30"/>
       <c r="G41" s="31"/>
       <c r="H41" s="32"/>
@@ -3728,8 +4288,8 @@
       <c r="C42" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="D42" s="29"/>
-      <c r="E42" s="29"/>
+      <c r="D42" s="58"/>
+      <c r="E42" s="58"/>
       <c r="F42" s="30"/>
       <c r="G42" s="31"/>
       <c r="H42" s="32"/>
@@ -3755,8 +4315,8 @@
       <c r="C43" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
+      <c r="D43" s="58"/>
+      <c r="E43" s="58"/>
       <c r="F43" s="30"/>
       <c r="G43" s="31"/>
       <c r="H43" s="32"/>
@@ -3780,8 +4340,8 @@
       <c r="A44" s="26"/>
       <c r="B44" s="27"/>
       <c r="C44" s="35"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="29"/>
+      <c r="D44" s="58"/>
+      <c r="E44" s="58"/>
       <c r="F44" s="30"/>
       <c r="G44" s="31"/>
       <c r="H44" s="32"/>
@@ -3805,8 +4365,8 @@
       <c r="A45" s="26"/>
       <c r="B45" s="27"/>
       <c r="C45" s="35"/>
-      <c r="D45" s="29"/>
-      <c r="E45" s="29"/>
+      <c r="D45" s="58"/>
+      <c r="E45" s="58"/>
       <c r="F45" s="30"/>
       <c r="G45" s="31"/>
       <c r="H45" s="32"/>
@@ -3830,8 +4390,8 @@
       <c r="A46" s="26"/>
       <c r="B46" s="27"/>
       <c r="C46" s="35"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
+      <c r="D46" s="58"/>
+      <c r="E46" s="58"/>
       <c r="F46" s="30"/>
       <c r="G46" s="31"/>
       <c r="H46" s="32"/>
@@ -3855,8 +4415,8 @@
       <c r="A47" s="26"/>
       <c r="B47" s="27"/>
       <c r="C47" s="35"/>
-      <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
+      <c r="D47" s="58"/>
+      <c r="E47" s="58"/>
       <c r="F47" s="30"/>
       <c r="G47" s="31"/>
       <c r="H47" s="32"/>
@@ -3882,8 +4442,8 @@
       <c r="C48" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="D48" s="29"/>
-      <c r="E48" s="29"/>
+      <c r="D48" s="58"/>
+      <c r="E48" s="58"/>
       <c r="F48" s="30"/>
       <c r="G48" s="31"/>
       <c r="H48" s="32"/>
@@ -3909,8 +4469,8 @@
       <c r="C49" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
+      <c r="D49" s="58"/>
+      <c r="E49" s="58"/>
       <c r="F49" s="30"/>
       <c r="G49" s="31"/>
       <c r="H49" s="32"/>
@@ -3936,8 +4496,8 @@
       <c r="C50" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="D50" s="29"/>
-      <c r="E50" s="29"/>
+      <c r="D50" s="58"/>
+      <c r="E50" s="58"/>
       <c r="F50" s="30"/>
       <c r="G50" s="31"/>
       <c r="H50" s="32"/>
@@ -3961,8 +4521,8 @@
       <c r="A51" s="26"/>
       <c r="B51" s="27"/>
       <c r="C51" s="35"/>
-      <c r="D51" s="29"/>
-      <c r="E51" s="29"/>
+      <c r="D51" s="58"/>
+      <c r="E51" s="58"/>
       <c r="F51" s="30"/>
       <c r="G51" s="31"/>
       <c r="H51" s="32"/>
@@ -3986,8 +4546,8 @@
       <c r="A52" s="26"/>
       <c r="B52" s="27"/>
       <c r="C52" s="35"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
+      <c r="D52" s="58"/>
+      <c r="E52" s="58"/>
       <c r="F52" s="30"/>
       <c r="G52" s="31"/>
       <c r="H52" s="32"/>
@@ -4530,7 +5090,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="41.54296875" customWidth="1"/>
@@ -4729,6 +5289,112 @@
       <c r="C14" s="46"/>
       <c r="D14" s="46" t="s">
         <v>167</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="45">
+        <v>3</v>
+      </c>
+      <c r="B15" s="45">
+        <v>1</v>
+      </c>
+      <c r="C15" s="46"/>
+      <c r="D15" s="46" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="45">
+        <v>3</v>
+      </c>
+      <c r="B16" s="45">
+        <v>2</v>
+      </c>
+      <c r="C16" s="46" t="s">
+        <v>223</v>
+      </c>
+      <c r="D16" s="46" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="45">
+        <v>3</v>
+      </c>
+      <c r="B17" s="45">
+        <v>3</v>
+      </c>
+      <c r="C17" s="46" t="s">
+        <v>224</v>
+      </c>
+      <c r="D17" s="46" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="45">
+        <v>3</v>
+      </c>
+      <c r="B18" s="45">
+        <v>4</v>
+      </c>
+      <c r="C18" s="46" t="s">
+        <v>225</v>
+      </c>
+      <c r="D18" s="46" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="45">
+        <v>3</v>
+      </c>
+      <c r="B19" s="45">
+        <v>5</v>
+      </c>
+      <c r="C19" s="46" t="s">
+        <v>226</v>
+      </c>
+      <c r="D19" s="46" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="50" x14ac:dyDescent="0.25">
+      <c r="A20" s="45">
+        <v>3</v>
+      </c>
+      <c r="B20" s="45">
+        <v>6</v>
+      </c>
+      <c r="C20" s="46"/>
+      <c r="D20" s="46" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="45">
+        <v>3</v>
+      </c>
+      <c r="B21" s="45">
+        <v>7</v>
+      </c>
+      <c r="C21" s="46" t="s">
+        <v>227</v>
+      </c>
+      <c r="D21" s="46" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="45">
+        <v>3</v>
+      </c>
+      <c r="B22" s="45">
+        <v>8</v>
+      </c>
+      <c r="C22" s="46"/>
+      <c r="D22" s="46" t="s">
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -4752,7 +5418,7 @@
     <col min="10" max="257" width="9.08984375" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="51" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="51" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="50" t="s">
         <v>78</v>
       </c>
@@ -4781,7 +5447,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="47" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="47" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="52">
         <v>1</v>
       </c>
@@ -4810,7 +5476,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="47" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" s="47" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="52">
         <v>2</v>
       </c>
@@ -4839,20 +5505,35 @@
         <v>171</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="47" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" s="47" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="52">
         <v>3</v>
       </c>
-      <c r="B4" s="52"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-    </row>
-    <row r="5" spans="1:9" s="47" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="52">
+        <v>3</v>
+      </c>
+      <c r="C4" s="52" t="s">
+        <v>214</v>
+      </c>
+      <c r="D4" s="60">
+        <v>46265</v>
+      </c>
+      <c r="E4" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="F4" s="53"/>
+      <c r="G4" s="52" t="s">
+        <v>236</v>
+      </c>
+      <c r="H4" s="54" t="s">
+        <v>237</v>
+      </c>
+      <c r="I4" s="57" t="s">
+        <v>238</v>
+      </c>
+      <c r="J4" s="53"/>
+    </row>
+    <row r="5" spans="1:10" s="47" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="52">
         <v>4</v>
       </c>
@@ -4865,7 +5546,7 @@
       <c r="H5" s="53"/>
       <c r="I5" s="53"/>
     </row>
-    <row r="6" spans="1:9" s="47" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" s="47" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="52">
         <v>5</v>
       </c>
@@ -4878,7 +5559,7 @@
       <c r="H6" s="53"/>
       <c r="I6" s="53"/>
     </row>
-    <row r="7" spans="1:9" s="47" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" s="47" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="52">
         <v>6</v>
       </c>
@@ -4891,7 +5572,7 @@
       <c r="H7" s="53"/>
       <c r="I7" s="53"/>
     </row>
-    <row r="8" spans="1:9" s="47" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" s="47" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="52">
         <v>7</v>
       </c>
